--- a/Task_01_population distribution.xlsx
+++ b/Task_01_population distribution.xlsx
@@ -8,31 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Internship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{556D8644-8CB8-45F2-AA57-F7B708BF1C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E72EEC-C79D-4B46-9365-E7110206AB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{A86AE97A-2E13-4DE7-86AD-578D313EDCB3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A86AE97A-2E13-4DE7-86AD-578D313EDCB3}"/>
   </bookViews>
   <sheets>
     <sheet name="API_SP.POP.TOTL_DS2_en_csv_v2_3" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet2!$A$1:$B$15</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet2!$C$1:$C$15</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet2!$D$1:$D$15</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet2!$H$14</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet2!$A$1:$B$15</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet2!$A$1:$D$15</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet2!$C$1:$C$15</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet2!$D$1:$D$15</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="538">
   <si>
     <t>Country Name</t>
   </si>
@@ -1647,9 +1636,6 @@
   <si>
     <t>ZWE</t>
   </si>
-  <si>
-    <t xml:space="preserve">Country Name </t>
-  </si>
 </sst>
 </file>
 
@@ -2262,7 +2248,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2483,7 +2469,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2669,98 +2655,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.5</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.6</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="1">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.5</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0"/>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{9975BC00-4649-49A6-98EC-763AEA9B8DF3}" formatIdx="0">
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:binning intervalClosed="r"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="clusteredColumn" hidden="1" uniqueId="{39E550D2-5EF8-44E4-BCDF-D80AB35C5384}" formatIdx="1">
-          <cx:dataId val="1"/>
-          <cx:layoutPr>
-            <cx:binning intervalClosed="r"/>
-          </cx:layoutPr>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0">
-        <cx:catScaling gapWidth="0"/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-      </cx:axis>
-    </cx:plotArea>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3303,514 +3198,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -3847,89 +3234,6 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>311421</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>138214</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>19591</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>145510</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="8" name="Chart 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B18537F-AE3E-0A20-0414-E17A5ED74018}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3959293" y="685395"/>
-              <a:ext cx="4572000" cy="2743200"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This chart isn't available in your version of Excel.
-Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -59887,225 +59191,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4E84D8-3E8D-4235-BD24-2088D32B602A}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>1960</v>
-      </c>
-      <c r="D1">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>54922</v>
-      </c>
-      <c r="D2">
-        <v>57619</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>130075728</v>
-      </c>
-      <c r="D3">
-        <v>144904094</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>9035043</v>
-      </c>
-      <c r="D4">
-        <v>9814318</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>97630925</v>
-      </c>
-      <c r="D5">
-        <v>106388440</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>5231654</v>
-      </c>
-      <c r="D6">
-        <v>5464187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>1608800</v>
-      </c>
-      <c r="D7">
-        <v>1814135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>9510</v>
-      </c>
-      <c r="D8">
-        <v>12764</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9">
-        <v>91540853</v>
-      </c>
-      <c r="D9">
-        <v>101729760</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10">
-        <v>131334</v>
-      </c>
-      <c r="D10">
-        <v>159692</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11">
-        <v>20386045</v>
-      </c>
-      <c r="D11">
-        <v>21769453</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12">
-        <v>1863705</v>
-      </c>
-      <c r="D12">
-        <v>2120135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13">
-        <v>20133</v>
-      </c>
-      <c r="D13">
-        <v>22673</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14">
-        <v>55603</v>
-      </c>
-      <c r="D14">
-        <v>59020</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15">
-        <v>10276477</v>
-      </c>
-      <c r="D15">
-        <v>11167000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/Task_01_population distribution.xlsx
+++ b/Task_01_population distribution.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Internship\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e0ea3d387f94b9c/Documents/GitHub/PRODIGY_DS_01/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E72EEC-C79D-4B46-9365-E7110206AB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
